--- a/www/download/COUNTRY.DNK.rpO2.xlsx
+++ b/www/download/COUNTRY.DNK.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Dinamarca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.59534474692871</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5.79710144928534</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>6.59587093480106</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>6.69075326805805</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>6.96718477441534</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>8.05866701654832</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>8.31600818352559</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>7.8696784336552</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6.5754865977623</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.98515681095156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5.98658985658789</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.94106463603802</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>5.4359641756125</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.07318051311202</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.34659312671883</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.553</t>
+          <t>-0.930998010764542</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.584</t>
+          <t>-0.92671806444882</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>-0.893574974630345</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>-0.900534444799858</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>-0.911756836450899</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>-0.924462597552204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.742</t>
+          <t>-0.930842985767891</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>-0.934759941660878</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>-0.940392834310595</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>-0.941953327323892</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.727</t>
+          <t>-0.947229178434632</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>-0.945799970749949</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>-0.936673581225643</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>-0.941081818817808</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>-0.900414975315651</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.352</t>
+          <t>-0.916256150229192</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.386</t>
+          <t>-0.911623387510143</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.434</t>
+          <t>-0.872409932730123</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>-0.88011290399396</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>-0.893847800159379</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>-0.908786247809011</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.561</t>
+          <t>-0.915975531415557</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.921393706917804</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>-0.928980788973072</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>-0.930905616382539</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.554</t>
+          <t>-0.937924816518722</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-0.936428928702995</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>-0.92473344070142</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>-0.930038407027758</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.651</t>
+          <t>-0.881772203152557</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3946.525</t>
+          <t>-0.897975012760272</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3968.857</t>
+          <t>-0.892247658493</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4069.596</t>
+          <t>-0.845357223519891</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4172.171</t>
+          <t>-0.853835260570586</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4237.91</t>
+          <t>-0.870070222660342</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4300.641</t>
+          <t>-0.887800331080555</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4354.175</t>
+          <t>-0.896464589150066</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4335.214</t>
+          <t>-0.903521865340971</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4278.018</t>
+          <t>-0.909230971135061</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4260.686</t>
+          <t>-0.910125904753476</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4305.218</t>
+          <t>-0.920564094213654</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4413.431</t>
+          <t>-0.915628821844194</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>4490.221</t>
+          <t>-0.90722741315499</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4563.611</t>
+          <t>-0.914651644320514</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4426.213</t>
+          <t>-0.857118030682611</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3561.707</t>
+          <t>133518939490.487</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3580.474</t>
+          <t>137811584300.214</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3694.916</t>
+          <t>110323480715.101</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3793.961</t>
+          <t>130934732477.287</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3866.816</t>
+          <t>137031408906.718</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3914.097</t>
+          <t>190472091107.522</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3978.711</t>
+          <t>216706358799.581</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3945.645</t>
+          <t>200976794623.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3897.167</t>
+          <t>236579381026.656</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3895.572</t>
+          <t>259912830756.824</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3953.214</t>
+          <t>306187914644.792</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4060.536</t>
+          <t>305797133958.861</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4152.28</t>
+          <t>272929858314.832</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4239.784</t>
+          <t>258316773472.211</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4075.162</t>
+          <t>155588552517.566</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>77132639386.6304</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>75661173253.8462</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>56192065723.0916</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>69843568644.4059</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>83680477882.0832</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>100520975444.427</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>116478484429.514</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>126990219698.842</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>139933004330.535</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>143513659674.447</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>165872063774.44</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>175790180398.219</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>156754830711.284</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>165767222520.149</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>100690356440.818</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>22622038.9972067</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>23251631.2702554</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>22250055.4568492</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>25965335.9866709</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>26849357.9119829</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>55.47</t>
+          <t>37014936.9330981</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>42439500.3472997</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>37790782.3318277</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>37391247.7424173</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>36450180.5545525</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>36663662.5964189</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>32175315.9983117</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>24487408.3094678</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>20328431.4066453</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>15653916.5667559</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>1592.47672927853</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>1696.89961933412</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1772.24900739836</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>2013.19528010808</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>1966.39165772062</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>1592.86748288294</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>1581.45166160118</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>1691.26202012543</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>1728.49696080776</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>1851.20866733458</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>1834.37443780109</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>2102.61348185028</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>2778.53045734769</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>2987.35654131626</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>3403.50279868531</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>55976.2296051148</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>59993.8561856547</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>47309.7113251972</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>55227.220322733</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>53822.1981542492</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>59003.3162240211</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>63852.2950975562</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>62227.6983532212</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>74892.3494181828</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>88874.1924953837</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>101207.617524437</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>107120.637245367</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>121845.577157707</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>129039.401024326</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>89763.9215323537</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>-0.917464598569614</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>-0.912941238403055</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>54.96</t>
+          <t>-0.874547483772435</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>-0.882499644962828</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55.53</t>
+          <t>-0.896111059938636</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>-0.910974795694859</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>-0.918323306871083</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>-0.923674747365266</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>-0.930468601213036</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>51.81</t>
+          <t>-0.932259544921366</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>-0.939029912692993</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>-0.937252007570364</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>-0.925733388826762</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>-0.931537793323359</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>-0.884294894674597</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>43861.1988105663</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>42639.5074734847</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>37539.4074308078</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>37095.3679527012</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>36258.1552354508</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>32077.3538309134</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>31029.8023038557</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>32682.0896666281</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>38628.7880709085</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>43816.496792744</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>43196.1392134982</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>44064.2666732117</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>49859.7500613318</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.59534474692871</t>
+          <t>32791.8265934315</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.79710144928534</t>
+          <t>31714.2015693576</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.59587093480106</t>
+          <t>23086.8643582945</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6.69075326805805</t>
+          <t>28189.5093259588</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.96718477441534</t>
+          <t>33419.6421075833</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.05866701654832</t>
+          <t>39775.6155701216</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.31600818352559</t>
+          <t>45488.2313796784</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.8696784336552</t>
+          <t>49612.9577533998</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.5754865977623</t>
+          <t>55307.105081455</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.98515681095156</t>
+          <t>56870.4945020966</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.98658985658789</t>
+          <t>64950.6713774369</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.94106463603802</t>
+          <t>67340.7942513566</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.4359641756125</t>
+          <t>58320.4997629245</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.07318051311202</t>
+          <t>60659.1842243302</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.34659312671883</t>
+          <t>37988.0794263212</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>138785115020.541</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>139569669457.722</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>102967301099.428</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>115156811230.314</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>161173261719.729</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>220038820070.277</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>251100951281.976</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>250194493091.694</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>289164123202.989</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>288314735498.178</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>337071974997.531</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>315417119815.877</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>265038229882.383</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>288009282371.305</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183272213452.027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>158895958671.555</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>158782614768.892</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>119346551741.311</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>132991528637.079</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>186235097149.599</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>273308891009.331</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>311027761278.049</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>311121607021.068</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>354156571867.74</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>363692881677.228</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>425525849087.173</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>409357547826.476</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>355511292780.814</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>379958217744.912</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>248535273469.987</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>-20110843651.0141</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-19212945311.1697</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>-16379250641.8829</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>-17834717406.7654</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>-25061835429.8701</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-53270070939.0544</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-59926809996.073</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-60927113929.3738</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>-64992448664.7512</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-75378146179.0505</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>-88453874089.6416</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>-93940428010.5991</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>-90473062898.431</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-91948935373.6064</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-65263060017.9596</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>2706.48657152449</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>2760.99911366417</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>2896.30522555254</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>3312.27735412384</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>3471.93119578696</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>3541.03230249282</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>3715.32831537514</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>3786.72153448461</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>3845.58037917119</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>3852.43317811895</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>3960.04810453108</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>4225.49964788984</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>4331.26587932205</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>4152.86160720256</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>4395.41473113229</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>2720.97878548521</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>2782.37710916725</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>2914.42982790617</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>3336.60594075938</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>3489.55892174841</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>3573.53444508413</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>3743.24576278775</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>3823.91823191249</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>3883.72479184002</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>3890.73472910819</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>3991.35085436021</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>4260.1285309779</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>4353.8433692175</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>4133.38915846487</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>4078.9150028037</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-93.1</t>
+          <t>63435.7198688412</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-92.67</t>
+          <t>64834.8321353354</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-89.36</t>
+          <t>59901.0402145433</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-90.05</t>
+          <t>59002.918688465</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-91.18</t>
+          <t>63789.1418136659</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>68026.8757360042</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-93.08</t>
+          <t>68753.7176463007</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-93.48</t>
+          <t>72415.7853827395</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>85723.8896220672</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-94.2</t>
+          <t>98085.0182609527</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-94.72</t>
+          <t>112538.837149356</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-94.58</t>
+          <t>128101.820149994</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>147311.572262702</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-94.11</t>
+          <t>172483.935431814</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>133160.800462652</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-91.63</t>
+          <t>54840733971.1053</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-91.16</t>
+          <t>57212756664.8131</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-87.24</t>
+          <t>45371286161.4543</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-88.01</t>
+          <t>49425535562.6707</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-89.38</t>
+          <t>60439561201.8897</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-90.88</t>
+          <t>84395408133.0091</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-91.6</t>
+          <t>94595118371.3035</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-92.14</t>
+          <t>88059383772.5154</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-92.9</t>
+          <t>103257961384.811</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-93.09</t>
+          <t>114651615694.405</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-93.79</t>
+          <t>144796043347.323</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-93.64</t>
+          <t>155723893911.894</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-92.47</t>
+          <t>134598311366.098</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-93</t>
+          <t>139811050837.444</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-88.18</t>
+          <t>80071515331.478</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-89.8</t>
+          <t>53811.4976921497</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-89.22</t>
+          <t>53513.5597832022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-84.54</t>
+          <t>50842.6571843734</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-85.38</t>
+          <t>52477.1155841272</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-87.01</t>
+          <t>52539.4291892659</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-88.78</t>
+          <t>56304.4997621318</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-89.65</t>
+          <t>56392.820255366</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>60285.701819875</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-90.92</t>
+          <t>69948.6046646054</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-91.01</t>
+          <t>83296.9080151088</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-92.06</t>
+          <t>96932.128610976</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-91.56</t>
+          <t>115795.462744549</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-90.72</t>
+          <t>135452.41609655</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-91.47</t>
+          <t>156527.12150155</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-85.71</t>
+          <t>117439.956803008</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6945.908</t>
+          <t>153775580264.776</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7189.985</t>
+          <t>151828138594.887</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7658.489</t>
+          <t>117229019103.625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8902.418</t>
+          <t>140080137580.634</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9399.884</t>
+          <t>166170668612.06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9693.198</t>
+          <t>222048119697.811</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10265.758</t>
+          <t>252587214499.905</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10500.327</t>
+          <t>250713897716.922</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10538.639</t>
+          <t>283156226733.829</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10495.809</t>
+          <t>309050003665.736</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10884.063</t>
+          <t>377823963710.514</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>11857.872</t>
+          <t>394858180761.776</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>12455.471</t>
+          <t>344923108996.62</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>12017.745</t>
+          <t>363479487471.138</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>11651.185</t>
+          <t>212378172071.331</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6366.173</t>
+          <t>9624.22217669158</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6586.968</t>
+          <t>11321.2723521332</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7049.436</t>
+          <t>9058.38303016988</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8206.644</t>
+          <t>6525.8031043378</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8693.476</t>
+          <t>11249.7126244</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8948.9</t>
+          <t>11722.3759738724</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9513.577</t>
+          <t>12360.8973909347</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9692.561</t>
+          <t>12130.0835628645</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>9729.738</t>
+          <t>15775.2849574618</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9721.681</t>
+          <t>14788.1102458439</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10113.234</t>
+          <t>15606.7085383796</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>11030.481</t>
+          <t>12306.3574054449</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>11641.65</t>
+          <t>11859.1561661517</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11348.79</t>
+          <t>15956.8139302642</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11650.388</t>
+          <t>15720.8436596438</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>133518.939</t>
+          <t>-98934846293.6703</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>137811.584</t>
+          <t>-94615381930.0738</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>110323.481</t>
+          <t>-71857732942.1705</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>130934.732</t>
+          <t>-90654602017.9632</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>137031.409</t>
+          <t>-105731107410.17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>190472.091</t>
+          <t>-137652711564.802</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>216706.359</t>
+          <t>-157992096128.601</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>200976.795</t>
+          <t>-162654513944.407</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>236579.381</t>
+          <t>-179898265349.019</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>259912.831</t>
+          <t>-194398387971.331</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>306187.915</t>
+          <t>-233027920363.192</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>305797.134</t>
+          <t>-239134286849.882</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>272929.858</t>
+          <t>-210324797630.522</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>258316.773</t>
+          <t>-223668436633.694</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>155588.553</t>
+          <t>-132306656739.853</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>76158.1308</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>77336.40736</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>71561.74027</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>71798.34376</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>72001.2481</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>68338.96983</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>67699.42724</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>72464.58774</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>87710.6187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>100475.73005</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>105203.46576</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>110691.77672</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>123787.42364</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>137405.3237</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>120509.42214</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3798.502</t>
+          <t>0.0139811336534613</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3897.94</t>
+          <t>0.0145448918318697</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4132.781</t>
+          <t>0.0187305684590437</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4772.958</t>
+          <t>0.0156126010177232</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5006.437</t>
+          <t>0.0173309104275905</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5142.03</t>
+          <t>0.0260410905227444</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5367.241</t>
+          <t>0.02530057128917</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5462.269</t>
+          <t>0.0249311535070664</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5460.194</t>
+          <t>0.026484276164611</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5413.865</t>
+          <t>0.0306657645992037</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5549.615</t>
+          <t>0.0339216693411881</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6002.328</t>
+          <t>0.0368486967378255</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6223.812</t>
+          <t>0.0334409342916807</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5980.222</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5899.32</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>94971.4486076223</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>96628.980039683</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>89063.7497972945</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>92950.5213038583</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>93612.2728596442</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>84412.844093664</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>86209.8718097497</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>94381.1111311811</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>115950.35382168</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>131238.165489814</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>137583.502637156</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>146652.503161933</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>170947.778596475</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>192843.389463581</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>184367.104605978</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>77132.639</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>75661.173</t>
+          <t>105475.073243332</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>56192.066</t>
+          <t>96758.6284176353</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69843.569</t>
+          <t>100831.035595434</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>83680.478</t>
+          <t>101218.949515811</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>100520.975</t>
+          <t>91433.6251083937</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>116478.484</t>
+          <t>93025.9601306236</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>126990.22</t>
+          <t>102246.71517741</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>139933.004</t>
+          <t>125590.118048088</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>143513.66</t>
+          <t>141688.54413748</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>165872.064</t>
+          <t>148070.084821056</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>175790.18</t>
+          <t>157652.834543269</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>156754.831</t>
+          <t>182898.0467475</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>165767.223</t>
+          <t>206255.911435343</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>100690.356</t>
+          <t>196642.801807363</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-91.75</t>
+          <t>715381.910500846</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-91.29</t>
+          <t>709772.477686175</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-87.45</t>
+          <t>632367.628214615</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>631824.896483757</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-89.61</t>
+          <t>617201.332464887</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-91.1</t>
+          <t>550681.842535283</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-91.83</t>
+          <t>545429.626777945</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-92.37</t>
+          <t>579962.246506701</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-93.05</t>
+          <t>696232.369591542</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-93.23</t>
+          <t>776989.753922345</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-93.9</t>
+          <t>806714.107145036</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-93.73</t>
+          <t>826951.669697429</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-92.57</t>
+          <t>937322.41144249</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-93.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-88.43</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22.622</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23.252</t>
+          <t>107478.314061647</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>110091.980918479</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25.965</t>
+          <t>115257.242471884</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>26.849</t>
+          <t>118907.260944611</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>37.015</t>
+          <t>122273.834383458</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>124968.864195211</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>37.791</t>
+          <t>127043.999053328</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>37.391</t>
+          <t>128545.372161906</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>129168.433981206</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>36.664</t>
+          <t>134200.158010163</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>32.175</t>
+          <t>139609.194989764</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>24.487</t>
+          <t>146197.708638013</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>20.328</t>
+          <t>148501.834772705</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>15.654</t>
+          <t>146718.272109112</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>94971.4486076223</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>98437.1041364147</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>101225.25690119</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>105795.945888027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>109542.071798057</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>112637.152021985</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>115656.904164777</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>116820.83945849</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>118078.377225152</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>119057.522886082</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>123814.229867481</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>129272.648164632</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>136062.616394368</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>137805.029282041</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>135438.121692759</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>53863.0489145471</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>52963.0713866682</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>49384.0125823647</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>46959.7979745664</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46954.8162441893</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>46417.7095416063</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>44829.4834593764</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>47141.2174625898</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>57067.9984219124</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>67643.4816825199</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>70561.2284089439</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>74536.3579667307</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>81204.6872324998</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>88539.9696946574</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>71286.3013226369</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6366173355.16077</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6586968044.45178</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>7049436036.98657</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8206644112.78081</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8693476150.99804</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8948900375.89216</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9513577428.87074</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9692560600.65442</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>9729737527.56443</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9721680616.34719</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10113234210.1211</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>11030480908.8319</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>11641650061.9618</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>11348789848.3873</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>11650388297.2373</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6945907849.19895</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>7189985205.83284</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7658489156.46477</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8902418330.17574</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>9399884190.01538</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9693197888.15294</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10265757923.3013</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10500326508.1024</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10538638687.9248</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10495809416.1009</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10884062540.9651</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>11857871800.0646</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>12455470756.8141</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>12017745376.5636</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>11651184677.6492</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3798501713.25438</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3897939552.59674</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4132781065.73301</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4772957680.74326</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5006436536.60586</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5142029630.50357</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5367240608.65051</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5462268871.72783</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5460193788.43355</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5413865055.072</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5549614718.00688</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6002327778.35613</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6223811661.75453</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5980222295.1922</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5899319736.67244</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2552724</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2584116</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2627783</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2668106</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2693717</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2712496</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2742475</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2745960</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2713539</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2697642</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2726912</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2783454</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2860799</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2907479.77406196</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2856442.13464624</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2352191</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2385719</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2433941</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2477644</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2503931</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2527201</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2560629</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2559618</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2530109</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2523517</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2553816</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2610456</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2687817</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2732763.79562092</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2650577.70651737</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3946525000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3968857000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4069596000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4172171000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4237910000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4300641000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4354175000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4335214000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4278018000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4260686000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4305218000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4413431000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4490221000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4563611344.86316</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4426213429.23584</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3561707000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3580474000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3694916000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3793961000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3866816000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3914097000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3978711000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3945645000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3897167000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3895572000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3953214000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4060536000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4152280000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4239783579</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4075161790.5794</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.223883473903054</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.23009214177032</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.236057132689494</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.245884667325644</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.250745961750358</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.255718720169047</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.263689990284609</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.268654797798724</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.299574972719611</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.302815111287093</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.313331495645102</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.318690099132054</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289584372171691</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.310858210514823</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.312893410037268</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.550590716553441</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.553503630601798</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.553976662936635</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.553250491018004</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.554990553961462</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.554732294142613</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.553521750790115</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.552981915247363</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.521002579797404</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.516869446873403</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.497784424326814</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.501836405989754</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466878590140647</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.466304492760894</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.450798377646792</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.225525809543505</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.216404227627882</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.209966204373871</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.200864841656351</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.19426348428818</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.18954898568834</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.182788258925276</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.178363286953914</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.179422447482985</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.180315441839504</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.188884080028084</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.179473494878193</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.243537037687662</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.222837296724283</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.236308212315941</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.184484225292462</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.191150044073375</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.197675761217595</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.204353656310667</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.208209712703704</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.209484889795474</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.216057403459574</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.223162201987542</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.249969179148038</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.252773922421227</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.265380467619703</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.268520250599075</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.240725825229757</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.264590109238242</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.266483772258316</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.543535941765506</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.547630426112232</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.549623609947919</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.551822541642323</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.555259003591729</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.557495429296252</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.557887924476222</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.55862712331648</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.523188138152505</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.518107901006387</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.500531128762789</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.498972650293365</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.463064097279716</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.462801473471055</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.446502858598185</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.271979832942032</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.261219529814393</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.252700628834487</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.24382380204701</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.236531283704567</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.233019680908274</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.226054672064205</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.218210674695979</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.226842682699457</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.229118176572386</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.234088403617508</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.23250709910756</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.296210077490528</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.272608417290703</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.287013369143499</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>298365.88747</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>300756.85585</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>278356.72166</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>283172.60081</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>285252.09168</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>269250.11318</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>273930.34712</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>295493.52028</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>357987.64963</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>410428.67847</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>444056.31049</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>484097.74638</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>561740.27321</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>630254.4631</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549075.19184</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>157483.05634</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>158438.14463</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>146142.641</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>147790.83357</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>148173.76576</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>137851.33465</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>137855.44359</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>149387.93264</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>182658.11647</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>209332.02582</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>218631.31323</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>232189.19251</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>264102.73398</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>294795.88113</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>267929.10313</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4002808.50525748</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4051529.22530515</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4122038.58445243</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4209363.92366684</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4297531.14459968</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4392592.39584807</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4488085.90693917</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4589482.40146926</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4676428.29878684</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4777350.63208677</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4898627.25363918</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5080876.73712512</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5275543.10240717</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
